--- a/output/graficos_nacionales/plot_nacional_d_depmenores_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_depmenores_a_2022.xlsx
@@ -103,24 +103,12 @@
     <t xml:space="preserve">Guaitecas</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11202</t>
   </si>
   <si>
     <t xml:space="preserve">Cisnes</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11301</t>
   </si>
   <si>
@@ -1171,6 +1159,12 @@
     <t xml:space="preserve">Concón</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">13132</t>
   </si>
   <si>
@@ -1429,6 +1423,12 @@
     <t xml:space="preserve">Ovalle</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">3101</t>
   </si>
   <si>
@@ -2167,7 +2167,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:16</t>
+    <t xml:space="preserve">2026-09-09 19:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2839,7 +2839,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>29.26</v>
+        <v>28.99</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>16</v>
@@ -2871,7 +2871,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>28.99</v>
+        <v>28.37</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>16</v>
@@ -2903,7 +2903,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>28.53</v>
+        <v>27.57</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2914,10 +2914,10 @@
         <v>2022</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>34</v>
@@ -2935,7 +2935,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.37</v>
+        <v>26.15</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2946,10 +2946,10 @@
         <v>2022</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>36</v>
@@ -2967,7 +2967,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>27.57</v>
+        <v>25.66</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2999,7 +2999,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>26.15</v>
+        <v>25.37</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -3031,7 +3031,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>25.66</v>
+        <v>24.75</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -3042,10 +3042,10 @@
         <v>2022</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>42</v>
@@ -3063,7 +3063,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>25.37</v>
+        <v>24.34</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -3074,10 +3074,10 @@
         <v>2022</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>44</v>
@@ -3095,7 +3095,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24.75</v>
+        <v>22.84</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -3127,7 +3127,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24.34</v>
+        <v>22.35</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -3138,10 +3138,10 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>48</v>
@@ -3159,7 +3159,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.84</v>
+        <v>17.61</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -3170,10 +3170,10 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>50</v>
@@ -3191,7 +3191,7 @@
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.35</v>
+        <v>14.02</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -3202,28 +3202,28 @@
         <v>2022</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>17.61</v>
+        <v>36.29</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -3234,28 +3234,28 @@
         <v>2022</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.02</v>
+        <v>35.71</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -3266,28 +3266,28 @@
         <v>2022</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>36.29</v>
+        <v>34.63</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3298,28 +3298,28 @@
         <v>2022</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>35.71</v>
+        <v>34.5</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3330,28 +3330,28 @@
         <v>2022</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>64</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>34.63</v>
+        <v>34.19</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3362,10 +3362,10 @@
         <v>2022</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>66</v>
@@ -3374,16 +3374,16 @@
         <v>67</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>34.5</v>
+        <v>34.19</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3397,7 +3397,7 @@
         <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>68</v>
@@ -3406,16 +3406,16 @@
         <v>69</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.19</v>
+        <v>33.98</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3426,28 +3426,28 @@
         <v>2022</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>34.19</v>
+        <v>33.9</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3458,28 +3458,28 @@
         <v>2022</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>33.98</v>
+        <v>33.77</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3490,10 +3490,10 @@
         <v>2022</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
@@ -3502,16 +3502,16 @@
         <v>76</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>33.9</v>
+        <v>33.16</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3522,28 +3522,28 @@
         <v>2022</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>33.77</v>
+        <v>33.05</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3554,28 +3554,28 @@
         <v>2022</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>33.16</v>
+        <v>32.89</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3586,10 +3586,10 @@
         <v>2022</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3598,16 +3598,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>33.05</v>
+        <v>32.4</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3618,10 +3618,10 @@
         <v>2022</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3630,16 +3630,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.89</v>
+        <v>32.39</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3650,10 +3650,10 @@
         <v>2022</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3662,16 +3662,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>32.4</v>
+        <v>32.39</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3682,10 +3682,10 @@
         <v>2022</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3694,16 +3694,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>32.39</v>
+        <v>32.11</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3714,10 +3714,10 @@
         <v>2022</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3726,16 +3726,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>32.39</v>
+        <v>31.77</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3746,10 +3746,10 @@
         <v>2022</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3758,16 +3758,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32.11</v>
+        <v>31.61</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3778,10 +3778,10 @@
         <v>2022</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3790,16 +3790,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>31.77</v>
+        <v>31.54</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3813,7 +3813,7 @@
         <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3822,16 +3822,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>31.61</v>
+        <v>31.36</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3842,10 +3842,10 @@
         <v>2022</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3854,16 +3854,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>31.54</v>
+        <v>31.23</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3877,7 +3877,7 @@
         <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3886,16 +3886,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>31.36</v>
+        <v>31.22</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3906,10 +3906,10 @@
         <v>2022</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3918,16 +3918,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>31.23</v>
+        <v>31.07</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3938,10 +3938,10 @@
         <v>2022</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
@@ -3950,16 +3950,16 @@
         <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>31.22</v>
+        <v>30.92</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3970,10 +3970,10 @@
         <v>2022</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>106</v>
@@ -3982,16 +3982,16 @@
         <v>107</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>31.07</v>
+        <v>30.92</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -4002,10 +4002,10 @@
         <v>2022</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
@@ -4014,16 +4014,16 @@
         <v>109</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>30.92</v>
+        <v>30.9</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -4034,10 +4034,10 @@
         <v>2022</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>110</v>
@@ -4046,16 +4046,16 @@
         <v>111</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>30.92</v>
+        <v>30.82</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -4069,7 +4069,7 @@
         <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>112</v>
@@ -4078,16 +4078,16 @@
         <v>113</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>30.9</v>
+        <v>30.65</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -4098,10 +4098,10 @@
         <v>2022</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>114</v>
@@ -4110,16 +4110,16 @@
         <v>115</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>30.82</v>
+        <v>30.61</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -4130,10 +4130,10 @@
         <v>2022</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>116</v>
@@ -4142,16 +4142,16 @@
         <v>117</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>30.65</v>
+        <v>30.49</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -4162,10 +4162,10 @@
         <v>2022</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>118</v>
@@ -4174,16 +4174,16 @@
         <v>119</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>30.61</v>
+        <v>30.47</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -4194,10 +4194,10 @@
         <v>2022</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>120</v>
@@ -4206,16 +4206,16 @@
         <v>121</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>30.49</v>
+        <v>30.41</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -4226,10 +4226,10 @@
         <v>2022</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>122</v>
@@ -4238,16 +4238,16 @@
         <v>123</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>30.47</v>
+        <v>30.4</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -4258,10 +4258,10 @@
         <v>2022</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>124</v>
@@ -4270,16 +4270,16 @@
         <v>125</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>30.41</v>
+        <v>30.37</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -4290,10 +4290,10 @@
         <v>2022</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>126</v>
@@ -4302,16 +4302,16 @@
         <v>127</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>30.4</v>
+        <v>30.37</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -4322,10 +4322,10 @@
         <v>2022</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>128</v>
@@ -4334,16 +4334,16 @@
         <v>129</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>30.37</v>
+        <v>30.11</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -4357,7 +4357,7 @@
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>130</v>
@@ -4366,16 +4366,16 @@
         <v>131</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>30.37</v>
+        <v>29.91</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -4386,10 +4386,10 @@
         <v>2022</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>132</v>
@@ -4398,16 +4398,16 @@
         <v>133</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>30.11</v>
+        <v>29.9</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -4418,10 +4418,10 @@
         <v>2022</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>134</v>
@@ -4430,16 +4430,16 @@
         <v>135</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>29.91</v>
+        <v>29.89</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4450,10 +4450,10 @@
         <v>2022</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>136</v>
@@ -4462,16 +4462,16 @@
         <v>137</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>29.9</v>
+        <v>29.87</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -4482,10 +4482,10 @@
         <v>2022</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>138</v>
@@ -4494,16 +4494,16 @@
         <v>139</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>29.89</v>
+        <v>29.87</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4514,10 +4514,10 @@
         <v>2022</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>140</v>
@@ -4526,16 +4526,16 @@
         <v>141</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>29.87</v>
+        <v>29.75</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4546,10 +4546,10 @@
         <v>2022</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
@@ -4558,16 +4558,16 @@
         <v>143</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>29.87</v>
+        <v>29.74</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4578,10 +4578,10 @@
         <v>2022</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>144</v>
@@ -4590,16 +4590,16 @@
         <v>145</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>29.75</v>
+        <v>29.71</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>16</v>
@@ -4610,10 +4610,10 @@
         <v>2022</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
@@ -4622,16 +4622,16 @@
         <v>147</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>29.74</v>
+        <v>29.67</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -4642,10 +4642,10 @@
         <v>2022</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>148</v>
@@ -4654,16 +4654,16 @@
         <v>149</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>29.71</v>
+        <v>29.64</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4674,10 +4674,10 @@
         <v>2022</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>150</v>
@@ -4686,16 +4686,16 @@
         <v>151</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>29.67</v>
+        <v>29.56</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4709,7 +4709,7 @@
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>152</v>
@@ -4718,16 +4718,16 @@
         <v>153</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>29.64</v>
+        <v>29.54</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4738,10 +4738,10 @@
         <v>2022</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>154</v>
@@ -4750,16 +4750,16 @@
         <v>155</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>29.56</v>
+        <v>29.52</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4770,10 +4770,10 @@
         <v>2022</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4782,16 +4782,16 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>29.54</v>
+        <v>29.5</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
@@ -4802,10 +4802,10 @@
         <v>2022</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4814,16 +4814,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>29.52</v>
+        <v>29.48</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4834,10 +4834,10 @@
         <v>2022</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4846,16 +4846,16 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>29.5</v>
+        <v>29.45</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -4866,10 +4866,10 @@
         <v>2022</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4878,16 +4878,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>29.48</v>
+        <v>29.41</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4898,10 +4898,10 @@
         <v>2022</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4910,16 +4910,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>29.45</v>
+        <v>29.37</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4930,10 +4930,10 @@
         <v>2022</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4942,16 +4942,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>29.41</v>
+        <v>29.35</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -4962,10 +4962,10 @@
         <v>2022</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4974,16 +4974,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>29.37</v>
+        <v>29.33</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
@@ -4994,10 +4994,10 @@
         <v>2022</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -5006,16 +5006,16 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>29.35</v>
+        <v>29.32</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
@@ -5026,10 +5026,10 @@
         <v>2022</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -5038,16 +5038,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>29.33</v>
+        <v>29.31</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -5061,7 +5061,7 @@
         <v>16</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -5070,16 +5070,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>29.32</v>
+        <v>29.29</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
@@ -5090,10 +5090,10 @@
         <v>2022</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -5102,16 +5102,16 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>29.31</v>
+        <v>29.23</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>16</v>
@@ -5122,10 +5122,10 @@
         <v>2022</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -5134,16 +5134,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>29.29</v>
+        <v>29.22</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -5154,10 +5154,10 @@
         <v>2022</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -5166,16 +5166,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>29.23</v>
+        <v>29.21</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -5186,10 +5186,10 @@
         <v>2022</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -5198,16 +5198,16 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>29.22</v>
+        <v>29.2</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -5218,10 +5218,10 @@
         <v>2022</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5230,16 +5230,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>29.21</v>
+        <v>29.18</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -5250,10 +5250,10 @@
         <v>2022</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5262,16 +5262,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>29.2</v>
+        <v>29.08</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -5282,10 +5282,10 @@
         <v>2022</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5294,16 +5294,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>29.18</v>
+        <v>29.08</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5314,10 +5314,10 @@
         <v>2022</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5326,10 +5326,10 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5346,10 +5346,10 @@
         <v>2022</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5358,16 +5358,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>29.08</v>
+        <v>29.01</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5381,7 +5381,7 @@
         <v>6</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5390,16 +5390,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>29.08</v>
+        <v>28.93</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>16</v>
@@ -5410,10 +5410,10 @@
         <v>2022</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5422,16 +5422,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>29.01</v>
+        <v>28.91</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5445,7 +5445,7 @@
         <v>6</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5454,16 +5454,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>28.93</v>
+        <v>28.91</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5474,10 +5474,10 @@
         <v>2022</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5486,16 +5486,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>28.91</v>
+        <v>28.9</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5509,7 +5509,7 @@
         <v>6</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5518,16 +5518,16 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>28.91</v>
+        <v>28.83</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
@@ -5538,10 +5538,10 @@
         <v>2022</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5550,16 +5550,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
@@ -5570,10 +5570,10 @@
         <v>2022</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5582,16 +5582,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>28.83</v>
+        <v>28.76</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5602,10 +5602,10 @@
         <v>2022</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5614,16 +5614,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.8</v>
+        <v>28.71</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5634,10 +5634,10 @@
         <v>2022</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5646,16 +5646,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>28.76</v>
+        <v>28.66</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5666,10 +5666,10 @@
         <v>2022</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5678,16 +5678,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>28.71</v>
+        <v>28.65</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5701,7 +5701,7 @@
         <v>6</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5710,16 +5710,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>28.66</v>
+        <v>28.57</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
@@ -5730,10 +5730,10 @@
         <v>2022</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5742,16 +5742,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>28.65</v>
+        <v>28.55</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
@@ -5762,10 +5762,10 @@
         <v>2022</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5774,16 +5774,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>28.57</v>
+        <v>28.54</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
@@ -5794,10 +5794,10 @@
         <v>2022</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5806,16 +5806,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>28.55</v>
+        <v>28.54</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5826,10 +5826,10 @@
         <v>2022</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5838,16 +5838,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>28.54</v>
+        <v>28.5</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
@@ -5858,10 +5858,10 @@
         <v>2022</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5870,16 +5870,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>28.54</v>
+        <v>28.5</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5890,10 +5890,10 @@
         <v>2022</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5902,10 +5902,10 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5922,10 +5922,10 @@
         <v>2022</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5934,16 +5934,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>28.5</v>
+        <v>28.35</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>16</v>
@@ -5954,10 +5954,10 @@
         <v>2022</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5966,16 +5966,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>28.5</v>
+        <v>28.33</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5989,7 +5989,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5998,16 +5998,16 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>28.35</v>
+        <v>28.28</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>16</v>
@@ -6018,10 +6018,10 @@
         <v>2022</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -6030,16 +6030,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>28.33</v>
+        <v>28.27</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -6050,10 +6050,10 @@
         <v>2022</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -6062,16 +6062,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>28.28</v>
+        <v>28.21</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
@@ -6085,7 +6085,7 @@
         <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -6094,16 +6094,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>28.27</v>
+        <v>28.2</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
@@ -6114,10 +6114,10 @@
         <v>2022</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6126,16 +6126,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>28.21</v>
+        <v>28.09</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>16</v>
@@ -6146,10 +6146,10 @@
         <v>2022</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6158,16 +6158,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>28.2</v>
+        <v>28.06</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
@@ -6178,10 +6178,10 @@
         <v>2022</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6190,16 +6190,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>28.09</v>
+        <v>27.99</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -6210,10 +6210,10 @@
         <v>2022</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6222,16 +6222,16 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>28.06</v>
+        <v>27.98</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
@@ -6242,10 +6242,10 @@
         <v>2022</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6254,16 +6254,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>27.99</v>
+        <v>27.96</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
@@ -6274,10 +6274,10 @@
         <v>2022</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6286,16 +6286,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>27.98</v>
+        <v>27.96</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
@@ -6306,10 +6306,10 @@
         <v>2022</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6318,16 +6318,16 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>27.96</v>
+        <v>27.93</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>16</v>
@@ -6338,10 +6338,10 @@
         <v>2022</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6350,16 +6350,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>27.96</v>
+        <v>27.89</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -6373,7 +6373,7 @@
         <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6382,16 +6382,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>27.93</v>
+        <v>27.87</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6402,10 +6402,10 @@
         <v>2022</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6414,16 +6414,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>27.89</v>
+        <v>27.83</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>16</v>
@@ -6437,7 +6437,7 @@
         <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6446,16 +6446,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>27.87</v>
+        <v>27.82</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6466,10 +6466,10 @@
         <v>2022</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6478,16 +6478,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>27.83</v>
+        <v>27.81</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6498,10 +6498,10 @@
         <v>2022</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6510,16 +6510,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>27.82</v>
+        <v>27.73</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>16</v>
@@ -6530,10 +6530,10 @@
         <v>2022</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6542,16 +6542,16 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>27.81</v>
+        <v>27.67</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>16</v>
@@ -6565,7 +6565,7 @@
         <v>5</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6574,16 +6574,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>27.73</v>
+        <v>27.64</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>16</v>
@@ -6597,7 +6597,7 @@
         <v>6</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6606,16 +6606,16 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>27.67</v>
+        <v>27.55</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>16</v>
@@ -6629,7 +6629,7 @@
         <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6638,16 +6638,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>27.64</v>
+        <v>27.52</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>16</v>
@@ -6658,10 +6658,10 @@
         <v>2022</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6670,16 +6670,16 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>27.55</v>
+        <v>27.47</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>16</v>
@@ -6693,7 +6693,7 @@
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6702,16 +6702,16 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>27.52</v>
+        <v>27.46</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -6722,10 +6722,10 @@
         <v>2022</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6734,16 +6734,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>27.47</v>
+        <v>27.44</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
@@ -6754,10 +6754,10 @@
         <v>2022</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6766,16 +6766,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>27.46</v>
+        <v>27.39</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -6786,10 +6786,10 @@
         <v>2022</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6798,16 +6798,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>27.44</v>
+        <v>27.38</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -6818,10 +6818,10 @@
         <v>2022</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6830,16 +6830,16 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>27.39</v>
+        <v>27.38</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>16</v>
@@ -6853,7 +6853,7 @@
         <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6862,16 +6862,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>27.38</v>
+        <v>27.34</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -6882,10 +6882,10 @@
         <v>2022</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6894,16 +6894,16 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>27.38</v>
+        <v>27.32</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6914,10 +6914,10 @@
         <v>2022</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6926,16 +6926,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>27.34</v>
+        <v>27.17</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6946,10 +6946,10 @@
         <v>2022</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6958,16 +6958,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>27.32</v>
+        <v>27.13</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6978,10 +6978,10 @@
         <v>2022</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6990,16 +6990,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>27.17</v>
+        <v>27.01</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -7010,10 +7010,10 @@
         <v>2022</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -7022,16 +7022,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>27.13</v>
+        <v>26.95</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -7042,10 +7042,10 @@
         <v>2022</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -7054,16 +7054,16 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>27.01</v>
+        <v>26.92</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -7074,10 +7074,10 @@
         <v>2022</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -7086,16 +7086,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>26.95</v>
+        <v>26.91</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -7106,10 +7106,10 @@
         <v>2022</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7118,16 +7118,16 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>26.92</v>
+        <v>26.91</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -7138,10 +7138,10 @@
         <v>2022</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7150,16 +7150,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>26.91</v>
+        <v>26.89</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -7170,10 +7170,10 @@
         <v>2022</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7182,16 +7182,16 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>26.91</v>
+        <v>26.82</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -7202,10 +7202,10 @@
         <v>2022</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7214,16 +7214,16 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>26.89</v>
+        <v>26.79</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -7237,7 +7237,7 @@
         <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7246,16 +7246,16 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>26.82</v>
+        <v>26.7</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>16</v>
@@ -7266,10 +7266,10 @@
         <v>2022</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7278,16 +7278,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>26.79</v>
+        <v>26.7</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -7301,7 +7301,7 @@
         <v>6</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7310,16 +7310,16 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>26.7</v>
+        <v>26.61</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
@@ -7330,10 +7330,10 @@
         <v>2022</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7342,16 +7342,16 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>16</v>
@@ -7362,10 +7362,10 @@
         <v>2022</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7374,16 +7374,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>26.61</v>
+        <v>26.48</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>16</v>
@@ -7397,7 +7397,7 @@
         <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7406,16 +7406,16 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>26.5</v>
+        <v>26.33</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7429,7 +7429,7 @@
         <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7438,16 +7438,16 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>26.48</v>
+        <v>26.28</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7458,10 +7458,10 @@
         <v>2022</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7470,16 +7470,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>26.33</v>
+        <v>26.28</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7490,10 +7490,10 @@
         <v>2022</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7502,16 +7502,16 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>26.28</v>
+        <v>26.24</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>16</v>
@@ -7522,10 +7522,10 @@
         <v>2022</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7534,16 +7534,16 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>26.28</v>
+        <v>26.16</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>16</v>
@@ -7557,7 +7557,7 @@
         <v>7</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7566,16 +7566,16 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>26.24</v>
+        <v>26.13</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7586,10 +7586,10 @@
         <v>2022</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7598,16 +7598,16 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>26.16</v>
+        <v>26.08</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7618,10 +7618,10 @@
         <v>2022</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7630,16 +7630,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>26.13</v>
+        <v>26.02</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
@@ -7650,10 +7650,10 @@
         <v>2022</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7662,16 +7662,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>26.08</v>
+        <v>25.76</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
@@ -7682,10 +7682,10 @@
         <v>2022</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7694,16 +7694,16 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>26.02</v>
+        <v>25.64</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>16</v>
@@ -7714,10 +7714,10 @@
         <v>2022</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7726,16 +7726,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>25.76</v>
+        <v>25.47</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
@@ -7746,10 +7746,10 @@
         <v>2022</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
@@ -7758,16 +7758,16 @@
         <v>343</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>25.64</v>
+        <v>25.46</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
@@ -7781,7 +7781,7 @@
         <v>5</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>344</v>
@@ -7790,16 +7790,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>25.47</v>
+        <v>25.44</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
@@ -7810,10 +7810,10 @@
         <v>2022</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>346</v>
@@ -7822,16 +7822,16 @@
         <v>347</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>25.46</v>
+        <v>25.4</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
@@ -7845,7 +7845,7 @@
         <v>5</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>348</v>
@@ -7854,16 +7854,16 @@
         <v>349</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>25.44</v>
+        <v>25.38</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>16</v>
@@ -7877,7 +7877,7 @@
         <v>16</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>350</v>
@@ -7886,16 +7886,16 @@
         <v>351</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>25.4</v>
+        <v>25.37</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
@@ -7906,10 +7906,10 @@
         <v>2022</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>352</v>
@@ -7918,16 +7918,16 @@
         <v>353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>25.38</v>
+        <v>25.35</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>16</v>
@@ -7938,10 +7938,10 @@
         <v>2022</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>354</v>
@@ -7950,16 +7950,16 @@
         <v>355</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>25.37</v>
+        <v>25.29</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>16</v>
@@ -7973,7 +7973,7 @@
         <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>356</v>
@@ -7982,16 +7982,16 @@
         <v>357</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>25.35</v>
+        <v>25.26</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>16</v>
@@ -8005,7 +8005,7 @@
         <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>358</v>
@@ -8014,16 +8014,16 @@
         <v>359</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>25.29</v>
+        <v>25.25</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>16</v>
@@ -8034,10 +8034,10 @@
         <v>2022</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>360</v>
@@ -8046,16 +8046,16 @@
         <v>361</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>25.26</v>
+        <v>25.19</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>16</v>
@@ -8066,10 +8066,10 @@
         <v>2022</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>362</v>
@@ -8078,16 +8078,16 @@
         <v>363</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>25.25</v>
+        <v>25.12</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>16</v>
@@ -8098,10 +8098,10 @@
         <v>2022</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>364</v>
@@ -8110,16 +8110,16 @@
         <v>365</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>25.19</v>
+        <v>25.07</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>16</v>
@@ -8130,10 +8130,10 @@
         <v>2022</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>366</v>
@@ -8142,16 +8142,16 @@
         <v>367</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>25.12</v>
+        <v>25.07</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>16</v>
@@ -8165,7 +8165,7 @@
         <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>368</v>
@@ -8174,16 +8174,16 @@
         <v>369</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>25.07</v>
+        <v>24.83</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>16</v>
@@ -8194,10 +8194,10 @@
         <v>2022</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>370</v>
@@ -8206,16 +8206,16 @@
         <v>371</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>25.07</v>
+        <v>24.79</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>16</v>
@@ -8229,7 +8229,7 @@
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>372</v>
@@ -8238,16 +8238,16 @@
         <v>373</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>24.83</v>
+        <v>24.72</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>16</v>
@@ -8261,7 +8261,7 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>374</v>
@@ -8270,16 +8270,16 @@
         <v>375</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>24.79</v>
+        <v>24.62</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>16</v>
@@ -8290,10 +8290,10 @@
         <v>2022</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>376</v>
@@ -8302,16 +8302,16 @@
         <v>377</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>24.72</v>
+        <v>24.59</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>16</v>
@@ -8322,10 +8322,10 @@
         <v>2022</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>378</v>
@@ -8334,16 +8334,16 @@
         <v>379</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>24.62</v>
+        <v>24.5</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>16</v>
@@ -8354,10 +8354,10 @@
         <v>2022</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>380</v>
@@ -8366,16 +8366,16 @@
         <v>381</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>24.59</v>
+        <v>24.34</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>16</v>
@@ -8386,10 +8386,10 @@
         <v>2022</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>382</v>
@@ -8398,16 +8398,16 @@
         <v>383</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>24.5</v>
+        <v>23.55</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>16</v>
@@ -8421,7 +8421,7 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>384</v>
@@ -8430,16 +8430,16 @@
         <v>385</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>23.55</v>
+        <v>23.3</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>16</v>
@@ -8453,7 +8453,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>386</v>
@@ -8462,16 +8462,16 @@
         <v>387</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>23.3</v>
+        <v>23.03</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>16</v>
@@ -8482,10 +8482,10 @@
         <v>2022</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>388</v>
@@ -8494,16 +8494,16 @@
         <v>389</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>23.03</v>
+        <v>22.62</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8514,10 +8514,10 @@
         <v>2022</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>390</v>
@@ -8526,16 +8526,16 @@
         <v>391</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>22.62</v>
+        <v>22.27</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8546,10 +8546,10 @@
         <v>2022</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>392</v>
@@ -8558,16 +8558,16 @@
         <v>393</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>22.27</v>
+        <v>20.29</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8581,7 +8581,7 @@
         <v>13</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>394</v>
@@ -8590,16 +8590,16 @@
         <v>395</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>20.29</v>
+        <v>20.2</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8613,7 +8613,7 @@
         <v>13</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>396</v>
@@ -8622,16 +8622,16 @@
         <v>397</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>20.2</v>
+        <v>19.65</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8645,7 +8645,7 @@
         <v>13</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>398</v>
@@ -8654,16 +8654,16 @@
         <v>399</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>19.65</v>
+        <v>17.62</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8677,7 +8677,7 @@
         <v>13</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>400</v>
@@ -8686,16 +8686,16 @@
         <v>401</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>17.62</v>
+        <v>15.23</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>16</v>
@@ -8706,28 +8706,28 @@
         <v>2022</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>56</v>
+        <v>402</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>59</v>
+        <v>405</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>60</v>
+        <v>406</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>15.23</v>
+        <v>46.78</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>16</v>
@@ -8741,25 +8741,25 @@
         <v>1</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D193" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F193" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="E193" s="2" t="s">
+      <c r="G193" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="F193" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>408</v>
-      </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>46.78</v>
+        <v>45.18</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>16</v>
@@ -8770,28 +8770,28 @@
         <v>2022</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>45.18</v>
+        <v>42.16</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>16</v>
@@ -8802,10 +8802,10 @@
         <v>2022</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>412</v>
@@ -8814,16 +8814,16 @@
         <v>413</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>42.16</v>
+        <v>39.07</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>16</v>
@@ -8834,28 +8834,28 @@
         <v>2022</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>39.07</v>
+        <v>38.67</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>16</v>
@@ -8866,28 +8866,28 @@
         <v>2022</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>38.67</v>
+        <v>38.52</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>16</v>
@@ -8898,10 +8898,10 @@
         <v>2022</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>420</v>
@@ -8910,16 +8910,16 @@
         <v>421</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>38.52</v>
+        <v>37.68</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>16</v>
@@ -8933,7 +8933,7 @@
         <v>1</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>422</v>
@@ -8942,16 +8942,16 @@
         <v>423</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>37.68</v>
+        <v>35.71</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>16</v>
@@ -8965,7 +8965,7 @@
         <v>1</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>424</v>
@@ -8974,16 +8974,16 @@
         <v>425</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>35.71</v>
+        <v>35.38</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>16</v>
@@ -8994,28 +8994,28 @@
         <v>2022</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>35.38</v>
+        <v>34.86</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>16</v>
@@ -9026,10 +9026,10 @@
         <v>2022</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>429</v>
@@ -9038,16 +9038,16 @@
         <v>430</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>34.86</v>
+        <v>34.16</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>16</v>
@@ -9061,7 +9061,7 @@
         <v>15</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>431</v>
@@ -9070,16 +9070,16 @@
         <v>432</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>34.16</v>
+        <v>33.63</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>16</v>
@@ -9090,10 +9090,10 @@
         <v>2022</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>433</v>
@@ -9102,16 +9102,16 @@
         <v>434</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>33.63</v>
+        <v>33.05</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>16</v>
@@ -9125,7 +9125,7 @@
         <v>2</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>435</v>
@@ -9134,16 +9134,16 @@
         <v>436</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>33.05</v>
+        <v>32.33</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>16</v>
@@ -9154,10 +9154,10 @@
         <v>2022</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>437</v>
@@ -9166,16 +9166,16 @@
         <v>438</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>32.33</v>
+        <v>31.97</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>16</v>
@@ -9189,7 +9189,7 @@
         <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>439</v>
@@ -9198,16 +9198,16 @@
         <v>440</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>31.97</v>
+        <v>31.69</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>16</v>
@@ -9221,7 +9221,7 @@
         <v>3</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>441</v>
@@ -9230,16 +9230,16 @@
         <v>442</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>31.69</v>
+        <v>31.38</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>16</v>
@@ -9253,7 +9253,7 @@
         <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>443</v>
@@ -9262,16 +9262,16 @@
         <v>444</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>31.38</v>
+        <v>31.35</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>16</v>
@@ -9282,10 +9282,10 @@
         <v>2022</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>445</v>
@@ -9294,16 +9294,16 @@
         <v>446</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>31.35</v>
+        <v>31.28</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>16</v>
@@ -9314,10 +9314,10 @@
         <v>2022</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>447</v>
@@ -9326,16 +9326,16 @@
         <v>448</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>31.28</v>
+        <v>31.04</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>16</v>
@@ -9346,10 +9346,10 @@
         <v>2022</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>449</v>
@@ -9358,16 +9358,16 @@
         <v>450</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>31.04</v>
+        <v>30.89</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>16</v>
@@ -9381,7 +9381,7 @@
         <v>2</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>451</v>
@@ -9390,16 +9390,16 @@
         <v>452</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>30.89</v>
+        <v>30.87</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>16</v>
@@ -9410,10 +9410,10 @@
         <v>2022</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>453</v>
@@ -9422,16 +9422,16 @@
         <v>454</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>30.87</v>
+        <v>30.51</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>16</v>
@@ -9442,10 +9442,10 @@
         <v>2022</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>455</v>
@@ -9454,16 +9454,16 @@
         <v>456</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>30.51</v>
+        <v>30.39</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>16</v>
@@ -9474,10 +9474,10 @@
         <v>2022</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>457</v>
@@ -9486,16 +9486,16 @@
         <v>458</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>30.39</v>
+        <v>30.33</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>16</v>
@@ -9506,28 +9506,28 @@
         <v>2022</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>459</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>460</v>
+        <v>414</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>30.33</v>
+        <v>30.31</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>16</v>
@@ -9541,25 +9541,25 @@
         <v>4</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D218" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="E218" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="F218" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>30.31</v>
+        <v>30.24</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>16</v>
@@ -9573,7 +9573,7 @@
         <v>4</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>462</v>
@@ -9582,16 +9582,16 @@
         <v>463</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>30.24</v>
+        <v>30.18</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>16</v>
@@ -9602,10 +9602,10 @@
         <v>2022</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>464</v>
@@ -9614,16 +9614,16 @@
         <v>465</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>30.18</v>
+        <v>30.14</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>16</v>
@@ -9634,10 +9634,10 @@
         <v>2022</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>466</v>
@@ -9646,16 +9646,16 @@
         <v>467</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>30.14</v>
+        <v>29.71</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>16</v>
@@ -9669,7 +9669,7 @@
         <v>4</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>468</v>
@@ -9678,16 +9678,16 @@
         <v>469</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>29.71</v>
+        <v>29.7</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>16</v>
@@ -9701,7 +9701,7 @@
         <v>3</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>470</v>
@@ -9710,10 +9710,10 @@
         <v>471</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9733,7 +9733,7 @@
         <v>4</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>472</v>
@@ -9742,10 +9742,10 @@
         <v>473</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9765,7 +9765,7 @@
         <v>4</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>474</v>
@@ -9774,10 +9774,10 @@
         <v>475</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9797,7 +9797,7 @@
         <v>2</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>476</v>
@@ -9806,10 +9806,10 @@
         <v>477</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9829,7 +9829,7 @@
         <v>4</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>478</v>
@@ -9838,10 +9838,10 @@
         <v>479</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9861,7 +9861,7 @@
         <v>2</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>480</v>
@@ -9870,10 +9870,10 @@
         <v>481</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9893,7 +9893,7 @@
         <v>4</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>482</v>
@@ -9902,10 +9902,10 @@
         <v>483</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9925,7 +9925,7 @@
         <v>4</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>484</v>
@@ -9934,10 +9934,10 @@
         <v>485</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
@@ -9957,7 +9957,7 @@
         <v>4</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>486</v>
@@ -9966,10 +9966,10 @@
         <v>487</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
@@ -9989,19 +9989,19 @@
         <v>2</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>488</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -10021,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>489</v>
@@ -10030,10 +10030,10 @@
         <v>490</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -10053,7 +10053,7 @@
         <v>4</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>491</v>
@@ -10062,10 +10062,10 @@
         <v>492</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -10085,7 +10085,7 @@
         <v>4</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>493</v>
@@ -10094,10 +10094,10 @@
         <v>494</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_d_depmenores_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_depmenores_a_2022.xlsx
@@ -2167,7 +2167,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:56</t>
+    <t xml:space="preserve">2026-09-15 11:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_d_depmenores_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_depmenores_a_2022.xlsx
@@ -2167,7 +2167,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-15 11:16</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
